--- a/r5-TC-FHIR-AG-Scheduling-R5-94-8---namen-der-interactions-wiederfinden/StructureDefinition-at-scheduling-schedule.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-94-8---namen-der-interactions-wiederfinden/StructureDefinition-at-scheduling-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T18:56:10+00:00</t>
+    <t>2026-02-24T18:31:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
